--- a/Vrindavanam Glassmorphism/Vrindavanam/cardamom.xlsx
+++ b/Vrindavanam Glassmorphism/Vrindavanam/cardamom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Glassmorphism\Vrindavanam Glassmorphism\Vrindavanam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD03ABE8-D541-4199-8C35-9BB4EA46282F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4A6191-2592-4BCB-80EC-B01B5B4534C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{213A37A3-F88C-42DF-B134-BBBC12CBE028}"/>
   </bookViews>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="77">
   <si>
     <t>Cardamom</t>
   </si>
@@ -180,12 +189,6 @@
     <t>Brown</t>
   </si>
   <si>
-    <t>750gm</t>
-  </si>
-  <si>
-    <t>800gm</t>
-  </si>
-  <si>
     <t>Natural aroma</t>
   </si>
   <si>
@@ -219,9 +222,6 @@
     <t>Dark green</t>
   </si>
   <si>
-    <t>850gm</t>
-  </si>
-  <si>
     <t>images/bold.jpg</t>
   </si>
   <si>
@@ -249,9 +249,6 @@
     <t>Pure aroma</t>
   </si>
   <si>
-    <t>Organic</t>
-  </si>
-  <si>
     <t>Natural</t>
   </si>
   <si>
@@ -259,16 +256,31 @@
   </si>
   <si>
     <t>variety_name</t>
+  </si>
+  <si>
+    <t>50gm</t>
+  </si>
+  <si>
+    <t>1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -611,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EDA5FEE-3D0D-4201-B43F-EBBD6EEA5F86}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -641,7 +653,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -685,13 +697,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
         <v>45</v>
@@ -700,7 +712,7 @@
         <v>46171</v>
       </c>
       <c r="I2">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -715,7 +727,7 @@
         <v>34</v>
       </c>
       <c r="N2">
-        <v>3500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -726,40 +738,40 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1">
         <v>46171</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
         <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="N3">
-        <v>2500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -770,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -782,28 +794,28 @@
         <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="I4">
-        <v>250</v>
+        <v>600</v>
       </c>
       <c r="J4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
         <v>17</v>
       </c>
       <c r="M4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="N4">
-        <v>9999</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -814,40 +826,40 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H5" s="1">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="I5">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N5">
-        <v>2000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -858,40 +870,40 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="H6" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="I6">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="J6">
         <v>9</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M6" t="s">
         <v>34</v>
       </c>
       <c r="N6">
-        <v>6750</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -902,40 +914,40 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="H7" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="I7">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M7" t="s">
         <v>34</v>
       </c>
       <c r="N7">
-        <v>3000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -946,40 +958,40 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="H8" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="I8">
+        <v>200</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8">
         <v>800</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8">
-        <v>4000</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -990,40 +1002,40 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="H9" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="I9">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N9">
-        <v>7200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1034,40 +1046,40 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H10" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="L10" t="s">
         <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="N10">
-        <v>5000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1078,40 +1090,40 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="H11" s="1">
-        <v>46176</v>
+        <v>46172</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="N11">
-        <v>3000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1122,43 +1134,1986 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I13">
+        <v>200</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I14">
+        <v>300</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I15">
+        <v>400</v>
+      </c>
+      <c r="J15">
+        <v>5</v>
+      </c>
+      <c r="K15" t="s">
+        <v>16</v>
+      </c>
+      <c r="L15" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I16">
+        <v>500</v>
+      </c>
+      <c r="J16">
+        <v>5</v>
+      </c>
+      <c r="K16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>17</v>
+      </c>
+      <c r="M17" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I18">
+        <v>200</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I19">
+        <v>300</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I20">
+        <v>400</v>
+      </c>
+      <c r="J20">
+        <v>5</v>
+      </c>
+      <c r="K20" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="M20" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I21">
+        <v>500</v>
+      </c>
+      <c r="J21">
+        <v>5</v>
+      </c>
+      <c r="K21" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" t="s">
+        <v>52</v>
+      </c>
+      <c r="N21">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I22">
+        <v>100</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G23" t="s">
+        <v>65</v>
+      </c>
+      <c r="H23" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I23">
+        <v>200</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>34</v>
+      </c>
+      <c r="N23">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H24" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I24">
+        <v>300</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M24" t="s">
+        <v>34</v>
+      </c>
+      <c r="N24">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I25">
+        <v>400</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s">
+        <v>65</v>
+      </c>
+      <c r="H26" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I26">
+        <v>500</v>
+      </c>
+      <c r="J26">
+        <v>4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I27">
+        <v>100</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" t="s">
+        <v>34</v>
+      </c>
+      <c r="N27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I28">
+        <v>200</v>
+      </c>
+      <c r="J28">
+        <v>3</v>
+      </c>
+      <c r="K28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" t="s">
+        <v>17</v>
+      </c>
+      <c r="M28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I29">
+        <v>300</v>
+      </c>
+      <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" t="s">
+        <v>34</v>
+      </c>
+      <c r="N29">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I30">
+        <v>400</v>
+      </c>
+      <c r="J30">
+        <v>4</v>
+      </c>
+      <c r="K30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" t="s">
+        <v>34</v>
+      </c>
+      <c r="N30">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s">
+        <v>59</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="1">
+        <v>46175</v>
+      </c>
+      <c r="I31">
+        <v>500</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="1">
+        <v>46176</v>
+      </c>
+      <c r="I32">
+        <v>100</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="1">
+        <v>46176</v>
+      </c>
+      <c r="I33">
+        <v>200</v>
+      </c>
+      <c r="J33">
+        <v>3</v>
+      </c>
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="1">
+        <v>46176</v>
+      </c>
+      <c r="I34">
+        <v>300</v>
+      </c>
+      <c r="J34">
+        <v>3</v>
+      </c>
+      <c r="K34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s">
+        <v>67</v>
+      </c>
+      <c r="H35" s="1">
+        <v>46176</v>
+      </c>
+      <c r="I35">
+        <v>400</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F36" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" s="1">
+        <v>46176</v>
+      </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36">
+        <v>4</v>
+      </c>
+      <c r="K36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I37">
+        <v>100</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>28</v>
+      </c>
+      <c r="L37" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" t="s">
+        <v>52</v>
+      </c>
+      <c r="N37">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I38">
+        <v>200</v>
+      </c>
+      <c r="J38">
+        <v>3</v>
+      </c>
+      <c r="K38" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38" t="s">
+        <v>17</v>
+      </c>
+      <c r="M38" t="s">
+        <v>52</v>
+      </c>
+      <c r="N38">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" t="s">
+        <v>32</v>
+      </c>
+      <c r="G39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I39">
+        <v>300</v>
+      </c>
+      <c r="J39">
+        <v>3</v>
+      </c>
+      <c r="K39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" t="s">
+        <v>17</v>
+      </c>
+      <c r="M39" t="s">
+        <v>52</v>
+      </c>
+      <c r="N39">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I40">
+        <v>400</v>
+      </c>
+      <c r="J40">
+        <v>4</v>
+      </c>
+      <c r="K40" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" t="s">
+        <v>17</v>
+      </c>
+      <c r="M40" t="s">
+        <v>52</v>
+      </c>
+      <c r="N40">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" t="s">
+        <v>30</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I41">
+        <v>500</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" t="s">
+        <v>17</v>
+      </c>
+      <c r="M41" t="s">
+        <v>52</v>
+      </c>
+      <c r="N41">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="E12" t="s">
+      <c r="B42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>39</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
+        <v>74</v>
+      </c>
+      <c r="G42" t="s">
+        <v>69</v>
+      </c>
+      <c r="H42" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I42">
+        <v>100</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" t="s">
+        <v>17</v>
+      </c>
+      <c r="M42" t="s">
+        <v>70</v>
+      </c>
+      <c r="N42">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G43" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I43">
+        <v>200</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="K43" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" t="s">
+        <v>70</v>
+      </c>
+      <c r="N43">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" t="s">
+        <v>69</v>
+      </c>
+      <c r="H44" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I44">
+        <v>300</v>
+      </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44" t="s">
+        <v>22</v>
+      </c>
+      <c r="L44" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" t="s">
+        <v>70</v>
+      </c>
+      <c r="N44">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" t="s">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s">
+        <v>69</v>
+      </c>
+      <c r="H45" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I45">
+        <v>400</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45" t="s">
+        <v>22</v>
+      </c>
+      <c r="L45" t="s">
+        <v>17</v>
+      </c>
+      <c r="M45" t="s">
+        <v>70</v>
+      </c>
+      <c r="N45">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" t="s">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46" s="1">
+        <v>46177</v>
+      </c>
+      <c r="I46">
+        <v>500</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+      <c r="K46" t="s">
+        <v>22</v>
+      </c>
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" t="s">
+        <v>70</v>
+      </c>
+      <c r="N46">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" t="s">
+        <v>63</v>
+      </c>
+      <c r="H47" s="1">
+        <v>46178</v>
+      </c>
+      <c r="I47">
+        <v>100</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47" t="s">
+        <v>33</v>
+      </c>
+      <c r="L47" t="s">
+        <v>29</v>
+      </c>
+      <c r="M47" t="s">
+        <v>76</v>
+      </c>
+      <c r="N47">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" t="s">
+        <v>72</v>
+      </c>
+      <c r="G48" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" s="1">
+        <v>46178</v>
+      </c>
+      <c r="I48">
+        <v>200</v>
+      </c>
+      <c r="J48">
+        <v>3</v>
+      </c>
+      <c r="K48" t="s">
+        <v>33</v>
+      </c>
+      <c r="L48" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48" t="s">
+        <v>76</v>
+      </c>
+      <c r="N48">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" t="s">
+        <v>50</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="G49" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" s="1">
+        <v>46178</v>
+      </c>
+      <c r="I49">
+        <v>300</v>
+      </c>
+      <c r="J49">
+        <v>3</v>
+      </c>
+      <c r="K49" t="s">
+        <v>33</v>
+      </c>
+      <c r="L49" t="s">
+        <v>29</v>
+      </c>
+      <c r="M49" t="s">
+        <v>76</v>
+      </c>
+      <c r="N49">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" s="1">
+        <v>46178</v>
+      </c>
+      <c r="I50">
+        <v>400</v>
+      </c>
+      <c r="J50">
+        <v>4</v>
+      </c>
+      <c r="K50" t="s">
+        <v>33</v>
+      </c>
+      <c r="L50" t="s">
+        <v>29</v>
+      </c>
+      <c r="M50" t="s">
+        <v>76</v>
+      </c>
+      <c r="N50">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F51" t="s">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" s="1">
+        <v>46178</v>
+      </c>
+      <c r="I51">
+        <v>500</v>
+      </c>
+      <c r="J51">
+        <v>4</v>
+      </c>
+      <c r="K51" t="s">
+        <v>33</v>
+      </c>
+      <c r="L51" t="s">
+        <v>29</v>
+      </c>
+      <c r="M51" t="s">
+        <v>76</v>
+      </c>
+      <c r="N51">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" t="s">
         <v>38</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F52" t="s">
+        <v>74</v>
+      </c>
+      <c r="G52" t="s">
+        <v>64</v>
+      </c>
+      <c r="H52" s="1">
+        <v>46179</v>
+      </c>
+      <c r="I52">
+        <v>100</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" t="s">
+        <v>71</v>
+      </c>
+      <c r="N52">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="G12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="1">
-        <v>46176</v>
-      </c>
-      <c r="I12">
-        <v>1000</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="B53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" t="s">
+        <v>72</v>
+      </c>
+      <c r="G53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H53" s="1">
+        <v>46179</v>
+      </c>
+      <c r="I53">
+        <v>200</v>
+      </c>
+      <c r="J53">
+        <v>3</v>
+      </c>
+      <c r="K53" t="s">
         <v>25</v>
       </c>
-      <c r="L12" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="L53" t="s">
+        <v>17</v>
+      </c>
+      <c r="M53" t="s">
+        <v>71</v>
+      </c>
+      <c r="N53">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" t="s">
+        <v>32</v>
+      </c>
+      <c r="G54" t="s">
+        <v>64</v>
+      </c>
+      <c r="H54" s="1">
+        <v>46179</v>
+      </c>
+      <c r="I54">
+        <v>300</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" t="s">
+        <v>71</v>
+      </c>
+      <c r="N54">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" s="1">
+        <v>46179</v>
+      </c>
+      <c r="I55">
+        <v>400</v>
+      </c>
+      <c r="J55">
+        <v>4</v>
+      </c>
+      <c r="K55" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+      <c r="M55" t="s">
+        <v>71</v>
+      </c>
+      <c r="N55">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
+      </c>
+      <c r="E56" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" t="s">
         <v>75</v>
       </c>
-      <c r="N12">
+      <c r="G56" t="s">
+        <v>64</v>
+      </c>
+      <c r="H56" s="1">
+        <v>46179</v>
+      </c>
+      <c r="I56">
+        <v>500</v>
+      </c>
+      <c r="J56">
+        <v>4</v>
+      </c>
+      <c r="K56" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" t="s">
+        <v>17</v>
+      </c>
+      <c r="M56" t="s">
+        <v>71</v>
+      </c>
+      <c r="N56">
         <v>2000</v>
       </c>
     </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H58" s="1"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>